--- a/assets/files/templates/SafePlum_tbm_log.xlsx
+++ b/assets/files/templates/SafePlum_tbm_log.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <r>
       <rPr>
@@ -671,9 +671,6 @@
   </si>
   <si>
     <t xml:space="preserve">일시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-27 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">작업 장소</t>
@@ -2303,13 +2300,13 @@
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>16</v>
+      <c r="B4" s="12" t="n">
+        <v>46322.3333333333</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
@@ -2318,15 +2315,15 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
@@ -2335,15 +2332,15 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>22</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -2352,7 +2349,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2365,10 +2362,10 @@
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -2380,10 +2377,10 @@
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -2395,7 +2392,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -2408,21 +2405,21 @@
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -2432,18 +2429,18 @@
         <v>1</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
@@ -2515,7 +2512,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -2529,14 +2526,14 @@
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="23"/>
       <c r="B22" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
       <c r="F22" s="23"/>
       <c r="G22" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -2544,14 +2541,14 @@
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="23"/>
       <c r="B23" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
       <c r="F23" s="23"/>
       <c r="G23" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H23" s="24"/>
       <c r="I23" s="24"/>
@@ -2559,21 +2556,21 @@
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="23"/>
       <c r="B24" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="23"/>
       <c r="G24" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2586,7 +2583,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -2599,7 +2596,7 @@
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -2612,29 +2609,29 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="I30" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2744,7 +2741,7 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>

--- a/assets/files/templates/SafePlum_tbm_log.xlsx
+++ b/assets/files/templates/SafePlum_tbm_log.xlsx
@@ -2199,12 +2199,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2217,12 +2217,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
